--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N4_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.78591934211204</v>
+        <v>1.773326698529147</v>
       </c>
       <c r="D2" t="n">
-        <v>22.25532432646658</v>
+        <v>1.956842138995533</v>
       </c>
       <c r="E2" t="n">
-        <v>2.633477142816669</v>
+        <v>5.903602682716293</v>
       </c>
       <c r="F2" t="n">
-        <v>6.849336420145688</v>
+        <v>9.962100712612493</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.81835350592894</v>
+        <v>13.78591934211204</v>
       </c>
       <c r="D3" t="n">
-        <v>27.77319089067781</v>
+        <v>22.25532432646658</v>
       </c>
       <c r="E3" t="n">
-        <v>2.633477142816669</v>
+        <v>5.903602682716293</v>
       </c>
       <c r="F3" t="n">
-        <v>6.849336420145688</v>
+        <v>9.962100712612493</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,23 +544,55 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>17.81835350592894</v>
+      </c>
+      <c r="D4" t="n">
+        <v>27.77319089067781</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.903602682716293</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.962100712612493</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T8387</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0075F0001T0006Z000C1N4.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>11.44174488039943</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>11.29291643075092</v>
       </c>
-      <c r="E4" t="n">
-        <v>2.633477142816669</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6.849336420145688</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>5.903602682716293</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.962100712612493</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>T8387</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.773326698529147</v>
+        <v>0.2881655885109864</v>
       </c>
       <c r="D2" t="n">
-        <v>1.956842138995533</v>
+        <v>0.3179868475867741</v>
       </c>
       <c r="E2" t="n">
-        <v>5.903602682716293</v>
+        <v>0.9593354359413976</v>
       </c>
       <c r="F2" t="n">
-        <v>9.962100712612493</v>
+        <v>1.61884136579953</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.78591934211204</v>
+        <v>2.240211893093206</v>
       </c>
       <c r="D3" t="n">
-        <v>22.25532432646658</v>
+        <v>3.616490203050819</v>
       </c>
       <c r="E3" t="n">
-        <v>5.903602682716293</v>
+        <v>0.9593354359413976</v>
       </c>
       <c r="F3" t="n">
-        <v>9.962100712612493</v>
+        <v>1.61884136579953</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.81835350592894</v>
+        <v>2.895482444713452</v>
       </c>
       <c r="D4" t="n">
-        <v>27.77319089067781</v>
+        <v>4.513143519735144</v>
       </c>
       <c r="E4" t="n">
-        <v>5.903602682716293</v>
+        <v>0.9593354359413976</v>
       </c>
       <c r="F4" t="n">
-        <v>9.962100712612493</v>
+        <v>1.61884136579953</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.44174488039943</v>
+        <v>1.859283543064907</v>
       </c>
       <c r="D5" t="n">
-        <v>11.29291643075092</v>
+        <v>1.835098919997025</v>
       </c>
       <c r="E5" t="n">
-        <v>5.903602682716293</v>
+        <v>0.9593354359413976</v>
       </c>
       <c r="F5" t="n">
-        <v>9.962100712612493</v>
+        <v>1.61884136579953</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
